--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7020"/>
   </bookViews>
   <sheets>
     <sheet name="SPV" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPV!$A$1:$C$257</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPV!$A$1:$C$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="125">
   <si>
     <t>SPV</t>
   </si>
@@ -405,477 +405,6 @@
   </si>
   <si>
     <t>IXS-IxtapanSal.pdv</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ACY-Acambay.pdv</t>
-  </si>
-  <si>
-    <t>ADJ-Almoloya.pdv</t>
-  </si>
-  <si>
-    <t>ALM-LasGlorias.pdv</t>
-  </si>
-  <si>
-    <t>ALT-Altec.pdv</t>
-  </si>
-  <si>
-    <t>ALZ-Alzeso.pdv</t>
-  </si>
-  <si>
-    <t>ATC-Jazmin.pdv</t>
-  </si>
-  <si>
-    <t>BLV-Bellavista.pdv</t>
-  </si>
-  <si>
-    <t>CAP-Capultitlan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Lagunilla.pdvc</t>
-  </si>
-  <si>
-    <t>COY-Coyotepec.pdv</t>
-  </si>
-  <si>
-    <t>CSG-CarlosG.pdv</t>
-  </si>
-  <si>
-    <t>CTM-Cuauhtemoc.pdv</t>
-  </si>
-  <si>
-    <t>DRZ-Chicahualco.pdv</t>
-  </si>
-  <si>
-    <t>ECT-ElCapulin.pdv</t>
-  </si>
-  <si>
-    <t>EJG-EricJaimes.pdv</t>
-  </si>
-  <si>
-    <t>JTP-Dexcani.pdv</t>
-  </si>
-  <si>
-    <t>LBT-Libertad.pdv</t>
-  </si>
-  <si>
-    <t>LML-Lazcano.pdv</t>
-  </si>
-  <si>
-    <t>LRC-Alarcon.pdv</t>
-  </si>
-  <si>
-    <t>LRM-Lerma.pdv</t>
-  </si>
-  <si>
-    <t>LZS-Jeronimo.pdv</t>
-  </si>
-  <si>
-    <t>MTP-Metepec.pdv</t>
-  </si>
-  <si>
-    <t>MXG-Mexicalzingo.pdv</t>
-  </si>
-  <si>
-    <t>OTT-Garcia.pdv</t>
-  </si>
-  <si>
-    <t>PAM-Manzana.pdv</t>
-  </si>
-  <si>
-    <t>PCH-ReformaMinS.pdv</t>
-  </si>
-  <si>
-    <t>PEC-PoligonoEct.pdv</t>
-  </si>
-  <si>
-    <t>POD-PorfirioDiaz.pdv</t>
-  </si>
-  <si>
-    <t>SAN-Barrio.pdv</t>
-  </si>
-  <si>
-    <t>SFE-SnFelipe.pdv</t>
-  </si>
-  <si>
-    <t>SGM-SergioM.pdv</t>
-  </si>
-  <si>
-    <t>SJG-SanJorge.pdv</t>
-  </si>
-  <si>
-    <t>SPA-SnPablo.pdv</t>
-  </si>
-  <si>
-    <t>TBZ-Tlalnepantla.pdv</t>
-  </si>
-  <si>
-    <t>THI-Tejupilco.pdv</t>
-  </si>
-  <si>
-    <t>TLC-Tolentino.pdv</t>
-  </si>
-  <si>
-    <t>TNC-Tianguistenco.pdv</t>
-  </si>
-  <si>
-    <t>TNN-Tenancingo.pdv</t>
-  </si>
-  <si>
-    <t>VBO-ValledeBravo.pdv</t>
-  </si>
-  <si>
-    <t>VCN-VillaCarbon.pdv</t>
-  </si>
-  <si>
-    <t>VDA-Allende.pdv</t>
-  </si>
-  <si>
-    <t>XHI-Xhitey.pdv</t>
-  </si>
-  <si>
-    <t>XLA-Xala.pdv</t>
-  </si>
-  <si>
-    <t>ZNC-Zinacantepec.pdv</t>
-  </si>
-  <si>
-    <t>R-001</t>
-  </si>
-  <si>
-    <t>AJR-Alejandro.pdv</t>
-  </si>
-  <si>
-    <t>BRN-Brandon.pdv</t>
-  </si>
-  <si>
-    <t>CHM-Chimalhuacan.pdv</t>
-  </si>
-  <si>
-    <t>CHN-Chicoloapan.pdv</t>
-  </si>
-  <si>
-    <t>CNC-Chiconcuac.pdv</t>
-  </si>
-  <si>
-    <t>GTA-Bucareli.pdv</t>
-  </si>
-  <si>
-    <t>LCC-LagChicoloapan.pdv</t>
-  </si>
-  <si>
-    <t>NER-Valle.pdv</t>
-  </si>
-  <si>
-    <t>NEZ-Neza.pdv</t>
-  </si>
-  <si>
-    <t>PTY-PaseoReyes.pdv</t>
-  </si>
-  <si>
-    <t>RDO-NardoNez.pdv</t>
-  </si>
-  <si>
-    <t>REY-Cancer.pdv</t>
-  </si>
-  <si>
-    <t>REY-Totolco.pdv</t>
-  </si>
-  <si>
-    <t>REY-Xochitenco.pdv</t>
-  </si>
-  <si>
-    <t>TEX-SanEsteban.pdv</t>
-  </si>
-  <si>
-    <t>TZY-Tezoyuca.pdv</t>
-  </si>
-  <si>
-    <t>R-002</t>
-  </si>
-  <si>
-    <t>AMC-Amecameca.pdv</t>
-  </si>
-  <si>
-    <t>BUA-Buenaventura.pdv</t>
-  </si>
-  <si>
-    <t>CDD-ChalcodeDiaz.pdv</t>
-  </si>
-  <si>
-    <t>COT-Cocotitlan.pdv</t>
-  </si>
-  <si>
-    <t>ETF-ElTriunfo.pdv</t>
-  </si>
-  <si>
-    <t>ITP-Ixtapaluca.pdv</t>
-  </si>
-  <si>
-    <t>MEC-Ameca.pdv</t>
-  </si>
-  <si>
-    <t>SOC-SolChalco.pdv</t>
-  </si>
-  <si>
-    <t>VAL-ValleChalco.pdv</t>
-  </si>
-  <si>
-    <t>ZAP-TizapanCha.pdv</t>
-  </si>
-  <si>
-    <t>R-003</t>
-  </si>
-  <si>
-    <t>BJR-Elvira.pdv</t>
-  </si>
-  <si>
-    <t>ECV-ElCalvario.pdv</t>
-  </si>
-  <si>
-    <t>LPP-GuadalupanaE.pdv</t>
-  </si>
-  <si>
-    <t>NEB-Bosques.pdv</t>
-  </si>
-  <si>
-    <t>ODA-OjodeAgua.pdv</t>
-  </si>
-  <si>
-    <t>PRI-Primavera.pdv</t>
-  </si>
-  <si>
-    <t>RUN-Rund.pdv</t>
-  </si>
-  <si>
-    <t>SNC-SantaClara.pdv</t>
-  </si>
-  <si>
-    <t>TCC-CdAzteca.pdv</t>
-  </si>
-  <si>
-    <t>TCC-CerroGdo.pdv</t>
-  </si>
-  <si>
-    <t>TCC-Estrella.pdv</t>
-  </si>
-  <si>
-    <t>TCC-LaPalma.pdv</t>
-  </si>
-  <si>
-    <t>TCC-Tecamac.pdv</t>
-  </si>
-  <si>
-    <t>TEO-SanLorenzo.pdv</t>
-  </si>
-  <si>
-    <t>TQX-Tequixquiac.pdv</t>
-  </si>
-  <si>
-    <t>VAR-ValleAragon.pdv</t>
-  </si>
-  <si>
-    <t>XAL-Xalostoc.pdv</t>
-  </si>
-  <si>
-    <t>ZUM-Zumpango.pdv</t>
-  </si>
-  <si>
-    <t>R-004</t>
-  </si>
-  <si>
-    <t>ACD-Acueducto.pdv</t>
-  </si>
-  <si>
-    <t>BRI-Brisas.pdv</t>
-  </si>
-  <si>
-    <t>CDB-Coacalco.pdv</t>
-  </si>
-  <si>
-    <t>CEY-CeylanTlane.pdv</t>
-  </si>
-  <si>
-    <t>FRG-Fragoso.pdv</t>
-  </si>
-  <si>
-    <t>GAM-Madero.pdv</t>
-  </si>
-  <si>
-    <t>JBO-Jacobo.pdv</t>
-  </si>
-  <si>
-    <t>MTM-MoisesT.pdv</t>
-  </si>
-  <si>
-    <t>OTB-Otumba.pdv</t>
-  </si>
-  <si>
-    <t>SYR-Syra.pdv</t>
-  </si>
-  <si>
-    <t>TBZ-GrupoZero.pdv</t>
-  </si>
-  <si>
-    <t>TBZ-JulioR.pdv</t>
-  </si>
-  <si>
-    <t>TLS-Toltecas.pdv</t>
-  </si>
-  <si>
-    <t>VDD-ValleDorado.pdv</t>
-  </si>
-  <si>
-    <t>R-005</t>
-  </si>
-  <si>
-    <t>CIN-Colinas.pdv</t>
-  </si>
-  <si>
-    <t>DRO-Dorado.pdv</t>
-  </si>
-  <si>
-    <t>EZN-EmilianoNac.pdv</t>
-  </si>
-  <si>
-    <t>GPZ-GpZero.pdv</t>
-  </si>
-  <si>
-    <t>JAS-JasaiN.pdv</t>
-  </si>
-  <si>
-    <t>LFS-LasFlores.pdv</t>
-  </si>
-  <si>
-    <t>MNL-ManuelS.pdv</t>
-  </si>
-  <si>
-    <t>SFC-SanFrancisco.pdv</t>
-  </si>
-  <si>
-    <t>STA-Guadalupe.pdv</t>
-  </si>
-  <si>
-    <t>TTO-Tlatilco.pdv</t>
-  </si>
-  <si>
-    <t>VES-VallesCin.pdv</t>
-  </si>
-  <si>
-    <t>R-006</t>
-  </si>
-  <si>
-    <t>BCI-BosqueCuati.pdv</t>
-  </si>
-  <si>
-    <t>CON-Convento.pdv</t>
-  </si>
-  <si>
-    <t>GIS-Girasoles.pdv</t>
-  </si>
-  <si>
-    <t>GZO-GZero.pdv</t>
-  </si>
-  <si>
-    <t>HEF-ElFaisan.pdv</t>
-  </si>
-  <si>
-    <t>JDM-Jardines.pdv</t>
-  </si>
-  <si>
-    <t>LMC-LomaCapulin.pdv</t>
-  </si>
-  <si>
-    <t>NAC-Echegaray.pdv</t>
-  </si>
-  <si>
-    <t>NIR-NicolasRomero.pdv</t>
-  </si>
-  <si>
-    <t>SIS-SnIsidro.pdv</t>
-  </si>
-  <si>
-    <t>STO-SantiagoIzcalli.pdv</t>
-  </si>
-  <si>
-    <t>VDS-VillaSol.pdv</t>
-  </si>
-  <si>
-    <t>R-007</t>
-  </si>
-  <si>
-    <t>ASG-Abasolo.pdv</t>
-  </si>
-  <si>
-    <t>CAN-Canarias.pdv</t>
-  </si>
-  <si>
-    <t>CTI-Cuautitlan.pdv</t>
-  </si>
-  <si>
-    <t>ECS-Ecos.pdv</t>
-  </si>
-  <si>
-    <t>FRE-Fresnos.pdv</t>
-  </si>
-  <si>
-    <t>HRS-Heroes.pdv</t>
-  </si>
-  <si>
-    <t>JAN-Jaltenco.pdv</t>
-  </si>
-  <si>
-    <t>MCO-Melchor.pdv</t>
-  </si>
-  <si>
-    <t>NEP-Nepantla.pdv</t>
-  </si>
-  <si>
-    <t>NLE-Naile.pdv</t>
-  </si>
-  <si>
-    <t>ORG-OrtegaEcatepec.pdv</t>
-  </si>
-  <si>
-    <t>RST-SaraT.pdv</t>
-  </si>
-  <si>
-    <t>TTP-Tultepec.pdv</t>
-  </si>
-  <si>
-    <t>TUN-Buenavista.pdv</t>
-  </si>
-  <si>
-    <t>R-C-008</t>
-  </si>
-  <si>
-    <t>AZN-ElPedregal.pdv</t>
-  </si>
-  <si>
-    <t>CLC-Aculco.pdv</t>
-  </si>
-  <si>
-    <t>CMK-Chirimikis.pdv</t>
-  </si>
-  <si>
-    <t>HXQ-Huixquilucan.pdv</t>
-  </si>
-  <si>
-    <t>JLT-Jilotzingo.pdv</t>
-  </si>
-  <si>
-    <t>LFL-LaFlorida.pdv</t>
-  </si>
-  <si>
-    <t>MRH-Maryhec.pdv</t>
-  </si>
-  <si>
-    <t>PLS-PaloSolo.pdv</t>
-  </si>
-  <si>
-    <t>TPN-Tepotzotlan.pdv</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +603,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1221,12 +750,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1245,42 +768,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1323,18 +822,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1386,19 +879,6 @@
         <color theme="4"/>
       </left>
       <right/>
-      <top style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4"/>
-      </right>
       <top style="thin">
         <color theme="4" tint="0.399975585192419"/>
       </top>
@@ -1531,7 +1011,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1543,34 +1023,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1597,65 +1077,65 @@
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1735,18 +1215,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2284,7 +1752,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C262"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="17.4285714285714" customWidth="1"/>
@@ -3511,1667 +2979,6 @@
       </c>
       <c r="C111" s="24" t="s">
         <v>124</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C112" s="25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C113" s="24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C114" s="25" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C115" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C116" s="25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C117" s="24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C118" s="25" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C119" s="24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C120" s="25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C121" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C122" s="25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C123" s="24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C124" s="25" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C125" s="24" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C126" s="25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C127" s="24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C128" s="25" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C129" s="24" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C130" s="25" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C131" s="24" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C132" s="25" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C133" s="24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C134" s="25" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C135" s="24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C136" s="25" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C137" s="24" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C138" s="25" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C139" s="24" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C140" s="25" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C141" s="24" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C142" s="25" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C143" s="24" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C144" s="25" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C145" s="24" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C146" s="25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C147" s="24" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C148" s="25" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C149" s="24" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C150" s="25" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C151" s="24" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C152" s="25" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C153" s="24" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C154" s="25" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C155" s="24" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C156" s="25" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C157" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C158" s="25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C159" s="24" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C160" s="25" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C161" s="24" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C162" s="25" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C163" s="24" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C164" s="25" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C165" s="24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C166" s="25" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C167" s="24" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C168" s="25" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C169" s="24" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C170" s="25" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C171" s="24" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C172" s="25" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3">
-      <c r="A173" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C173" s="24" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3">
-      <c r="A174" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C174" s="25" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C175" s="24" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C176" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C177" s="24" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C178" s="25" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C179" s="24" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="A180" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C180" s="25" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3">
-      <c r="A181" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C181" s="24" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C182" s="25" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C183" s="24" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C184" s="25" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C185" s="24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C186" s="25" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C187" s="24" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C188" s="25" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C189" s="24" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C190" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C191" s="24" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C192" s="25" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C193" s="24" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C194" s="25" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="A195" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C195" s="24" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3">
-      <c r="A196" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C196" s="25" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3">
-      <c r="A197" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C197" s="24" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="A198" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C198" s="25" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C199" s="24" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C200" s="25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C201" s="24" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="A202" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C202" s="25" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C203" s="26" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C204" s="25" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C205" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C206" s="25" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3">
-      <c r="A207" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C207" s="24" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C208" s="25" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3">
-      <c r="A209" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C209" s="24" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3">
-      <c r="A210" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C210" s="25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3">
-      <c r="A211" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C211" s="24" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3">
-      <c r="A212" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C212" s="25" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3">
-      <c r="A213" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C213" s="24" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C214" s="25" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3">
-      <c r="A215" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C215" s="24" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3">
-      <c r="A216" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C216" s="27" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3">
-      <c r="A217" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C217" s="24" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3">
-      <c r="A218" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C218" s="25" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3">
-      <c r="A219" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C219" s="24" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3">
-      <c r="A220" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C220" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3">
-      <c r="A221" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C221" s="24" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3">
-      <c r="A222" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C222" s="25" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3">
-      <c r="A223" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C223" s="24" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3">
-      <c r="A224" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C224" s="25" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3">
-      <c r="A225" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C225" s="24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
-      <c r="A226" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C226" s="25" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3">
-      <c r="A227" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C227" s="24" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3">
-      <c r="A228" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C228" s="25" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3">
-      <c r="A229" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C229" s="24" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C230" s="27" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3">
-      <c r="A231" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C231" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3">
-      <c r="A232" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C232" s="25" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
-      <c r="A233" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C233" s="24" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3">
-      <c r="A234" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C234" s="25" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3">
-      <c r="A235" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C235" s="24" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C236" s="25" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C237" s="24" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C238" s="25" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C239" s="24" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C240" s="25" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C241" s="24" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C242" s="25" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C243" s="25" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C244" s="24" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C245" s="27" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C246" s="24" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C247" s="24" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C248" s="25" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C249" s="24" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C250" s="25" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C251" s="24" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3">
-      <c r="A252" t="s">
-        <v>125</v>
-      </c>
-      <c r="B252" t="s">
-        <v>257</v>
-      </c>
-      <c r="C252" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3">
-      <c r="A253" t="s">
-        <v>125</v>
-      </c>
-      <c r="B253" t="s">
-        <v>257</v>
-      </c>
-      <c r="C253" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3">
-      <c r="A254" t="s">
-        <v>125</v>
-      </c>
-      <c r="B254" t="s">
-        <v>272</v>
-      </c>
-      <c r="C254" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3">
-      <c r="A255" t="s">
-        <v>125</v>
-      </c>
-      <c r="B255" t="s">
-        <v>272</v>
-      </c>
-      <c r="C255" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="A256" t="s">
-        <v>125</v>
-      </c>
-      <c r="B256" t="s">
-        <v>272</v>
-      </c>
-      <c r="C256" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3">
-      <c r="A257" t="s">
-        <v>125</v>
-      </c>
-      <c r="B257" t="s">
-        <v>272</v>
-      </c>
-      <c r="C257" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3">
-      <c r="A258" t="s">
-        <v>125</v>
-      </c>
-      <c r="B258" t="s">
-        <v>272</v>
-      </c>
-      <c r="C258" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259" t="s">
-        <v>125</v>
-      </c>
-      <c r="B259" t="s">
-        <v>272</v>
-      </c>
-      <c r="C259" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3">
-      <c r="A260" t="s">
-        <v>125</v>
-      </c>
-      <c r="B260" t="s">
-        <v>272</v>
-      </c>
-      <c r="C260" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3">
-      <c r="A261" t="s">
-        <v>125</v>
-      </c>
-      <c r="B261" t="s">
-        <v>272</v>
-      </c>
-      <c r="C261" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3">
-      <c r="A262" t="s">
-        <v>125</v>
-      </c>
-      <c r="B262" t="s">
-        <v>272</v>
-      </c>
-      <c r="C262" t="s">
-        <v>281</v>
       </c>
     </row>
   </sheetData>
